--- a/Practical-7thJuly.xlsx
+++ b/Practical-7thJuly.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Devanshu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Devanshu\Desktop\Python\jupyter projects\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E93611E-C56E-46BB-B5EA-7EAD326DDC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2213190-ED1D-4CAF-A37E-B63FC1F0D3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -527,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -543,7 +543,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,379 +637,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <c:style val="2"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-GB" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Product-wise Total Sales</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>Answers!#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredSeriesTitle>
-                <c15:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Answers!#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>#REF!</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c15:tx>
-              </c15:filteredSeriesTitle>
-            </c:ext>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredCategoryTitle>
-                <c15:cat>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Answers!#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                  </c:numRef>
-                </c15:cat>
-              </c15:filteredCategoryTitle>
-            </c:ext>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-215A-48D0-A32A-2FE73F8695EE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="71619553"/>
-        <c:axId val="32500551"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="71619553"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Product</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="32500551"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="32500551"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="B3B3B3"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Total Sales</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="71619553"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -1393,44 +1019,948 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Practical-7thJuly.xlsx]Answers!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Answers!$C$126</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Answers!$B$127:$B$130</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Mobile</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Answers!$C$127:$C$130</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>54000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D90F-4AA1-B87C-B0C6E0BDA4BA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="114287679"/>
+        <c:axId val="18633871"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="114287679"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="18633871"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="18633871"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="114287679"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>42120</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>24900</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1450,6 +1980,42 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>670560</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4978B6D-AACB-27A3-FF1E-97E9C36C2602}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1629,7 +2195,78 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED2F5BCE-E520-4403-B47F-CB1834F35806}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13DC8A72-0E7F-47CB-9C7B-B2BC386EE17A}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="B126:C130" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED2F5BCE-E520-4403-B47F-CB1834F35806}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B134:C139" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -1669,66 +2306,6 @@
     </i>
     <i>
       <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13DC8A72-0E7F-47CB-9C7B-B2BC386EE17A}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B126:C130" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -3786,7 +4363,7 @@
       <c r="B127" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127">
         <v>225000</v>
       </c>
       <c r="G127"/>
@@ -3795,7 +4372,7 @@
       <c r="B128" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C128" s="11">
+      <c r="C128">
         <v>135000</v>
       </c>
       <c r="G128"/>
@@ -3804,7 +4381,7 @@
       <c r="B129" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129">
         <v>54000</v>
       </c>
       <c r="G129"/>
@@ -3813,7 +4390,7 @@
       <c r="B130" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C130" s="11">
+      <c r="C130">
         <v>414000</v>
       </c>
       <c r="G130"/>
@@ -3851,7 +4428,7 @@
       <c r="B135" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135">
         <v>54000</v>
       </c>
       <c r="G135"/>
@@ -3860,7 +4437,7 @@
       <c r="B136" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C136" s="11">
+      <c r="C136">
         <v>150000</v>
       </c>
       <c r="G136"/>
@@ -3869,7 +4446,7 @@
       <c r="B137" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137">
         <v>165000</v>
       </c>
       <c r="G137"/>
@@ -3878,7 +4455,7 @@
       <c r="B138" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C138" s="11">
+      <c r="C138">
         <v>45000</v>
       </c>
       <c r="G138"/>
@@ -3887,7 +4464,7 @@
       <c r="B139" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139">
         <v>414000</v>
       </c>
       <c r="G139"/>
